--- a/output/pdf_financials_xlsx/FFC.P.xlsx
+++ b/output/pdf_financials_xlsx/FFC.P.xlsx
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000257</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>-0.045268</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.045268</v>
+        <v>-0.045011</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>-0.045268</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.045268</v>
+        <v>-0.045011</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.245837</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.216489</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.170945</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.245837</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.216489</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.170945</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">

--- a/output/pdf_financials_xlsx/FFC.P.xlsx
+++ b/output/pdf_financials_xlsx/FFC.P.xlsx
@@ -1134,7 +1134,7 @@
         <v>0.245837</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.216489</v>
+        <v>0.170945</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.170945</v>
@@ -1176,7 +1176,7 @@
         <v>0.245837</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.216489</v>
+        <v>0.170945</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.170945</v>
@@ -1761,7 +1761,7 @@
         <v>0.245837</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.216489</v>
+        <v>0.170945</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>0.170945</v>
@@ -1866,7 +1866,7 @@
         <v>0.011027</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.013987</v>
+        <v>0.013711</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.013711</v>
@@ -2283,7 +2283,7 @@
         <v>0.011027</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>0.013987</v>
+        <v>0.013711</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>0.013711</v>
@@ -2430,7 +2430,7 @@
         <v>0.23481</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.202502</v>
+        <v>0.157234</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>0.157234</v>
@@ -2472,7 +2472,7 @@
         <v>0.23481</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.202502</v>
+        <v>0.157234</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>0.157234</v>
@@ -2493,7 +2493,7 @@
         <v>0.9551450758022593</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.9353916365265672</v>
+        <v>0.9197929158501272</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>0.9197929158501272</v>
@@ -3241,7 +3241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3298,29 +3298,25 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Current assets</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0.245837</v>
+          <t>AS AT JULY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.216489</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.170945</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3341,22 +3337,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Cash 113,716</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.245837</v>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.216489</v>
-      </c>
-      <c r="G3" s="5" t="n">
         <v>0.170945</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -3372,27 +3372,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Notes 4 and 6)</t>
+          <t>Total assets 113,716</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.011027</v>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.013987</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.013711</v>
+        <v>0.170945</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -3413,22 +3417,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Accounts payable and accrued liabilities (Notes 4 and 6) 13,361</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0.011027</v>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.013987</v>
-      </c>
-      <c r="G5" s="5" t="n">
         <v>0.013711</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3444,27 +3452,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Share capital (Note 5)</t>
+          <t>Total liabilities 13,361</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.303981</v>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.328354</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.328354</v>
+        <v>0.013711</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3485,18 +3497,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Equity reserves (Note 5)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="5" t="n">
-        <v>0.047231</v>
+          <t>Share capital (Note 5) 328,354</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.037858</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.037858</v>
+        <v>0.328354</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3517,22 +3537,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>-0.116402</v>
+          <t>Equity reserves (Note 5) 37,858</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.16371</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-0.208978</v>
+        <v>0.037858</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3553,22 +3573,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.23481</v>
+          <t>Deficit (265,857)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.202502</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.157234</v>
+        <v>-0.208978</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3589,22 +3609,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity</t>
+          <t>Total shareholders’ equity 100,355</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0.245837</v>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.216489</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.170945</v>
+        <v>0.157234</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3615,22 +3639,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Total liabilities and shareholders’ equity 113,716</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3639,226 +3663,228 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.047308</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>-0.045268</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>-0.056879</v>
+        <v>0.170945</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>-0.002511</v>
+          <t>Basis of presentation (Note</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.00296</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>-0.000276</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>-0.00035</v>
+        <v>2e-06</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.051377</v>
+        <v>0.245837</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-0.044348</v>
+        <v>0.216489</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.045544</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>-0.057229</v>
+        <v>0.170945</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.245837</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.216489</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.045544</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>-0.057229</v>
+        <v>0.170945</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Accounts payable and accrued liabilities (Notes 4 and 6)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.011027</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.013987</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.216489</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>0.170945</v>
+        <v>0.013711</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.011027</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.013987</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.170945</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0.113716</v>
+        <v>0.013711</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Proceeds from share issuance</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital (Note 5)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.303981</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.328354</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.328354</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3869,36 +3895,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Equity reserves (Note 5)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>0.047231</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.037858</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.037858</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3909,32 +3927,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.08418</v>
+        <v>-0.116402</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.029348</v>
+        <v>-0.16371</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.045544</v>
+        <v>-0.208978</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -3945,32 +3963,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Total shareholders’ equity</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.330017</v>
+        <v>0.23481</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.245837</v>
+        <v>0.202502</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.216489</v>
+        <v>0.157234</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3981,22 +3999,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Total liabilities and shareholders’ equity</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -4027,7 +4045,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4035,21 +4053,19 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>-0.048866</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
         <v>-0.047308</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G22" s="5" t="n">
+        <v>-0.045268</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.056879</v>
       </c>
     </row>
     <row r="23">
@@ -4060,36 +4076,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Payments for share issuance costs</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-0.032803</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002511</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.00296</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.000276</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.00035</v>
       </c>
     </row>
     <row r="24">
@@ -4100,34 +4110,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Net cash provided by (used in) financing activities</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.032803</v>
+        <v>-0.051377</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.044348</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.045544</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.057229</v>
       </c>
     </row>
     <row r="25">
@@ -4138,83 +4144,93 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>equity reserve to share capital.</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>equity reserve to share capital. payable and accrued liabilities as at July</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.045544</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>-0.057229</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital item</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FOR THE YEARS ENDED JULY</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.216489</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.170945</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Professional fees 28,099</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4222,44 +4238,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>0.011102</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.170945</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.113716</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Administrative and corporate services (Note 6) 18,900</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Proceeds from share issuance</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.015</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4275,22 +4293,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and filing fees 13,517</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4299,7 +4317,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.015523</v>
+        <v>0.015</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4315,32 +4333,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Interest income (3,637)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-0.08418</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-0.000257</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.029348</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.045544</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4351,36 +4369,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year (56,879)</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.330017</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.045268</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.245837</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.216489</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4391,32 +4405,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 5) (0.02)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.245837</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.216489</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.170945</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4427,27 +4441,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 3,630,000 328,354 37,858 (163,710)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>-0.048866</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.202502</v>
+        <v>-0.047308</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4463,27 +4479,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (45,268)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>-0.045268</v>
+          <t>Payments for share issuance costs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>-0.032803</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4499,27 +4519,29 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2024 3,630,000 328,354 37,858 (208,978)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>-0.032803</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.157234</v>
+        <v>0.015</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4535,27 +4557,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>equity reserve to share capital.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (56,879)</t>
+          <t>equity reserve to share capital. payable and accrued liabilities as at July</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E36" s="5" t="n">
+        <v>0.002021</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.056879</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4574,14 +4594,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2025 3,630,000 328,354 37,858 (265,857)</t>
+          <t>FOR THE YEARS ENDED JULY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -4591,7 +4607,7 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.100355</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4617,18 +4633,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Administrative and corporate services (Note 6)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="n">
-        <v>0.0189</v>
+          <t>Professional fees 28,099</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.0189</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.011102</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4644,27 +4668,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.015279</v>
+          <t>Administrative and corporate services (Note 6) 18,900</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.01467</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.015523</v>
+        <v>0.0189</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4685,22 +4709,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Transfer  agent, shareholder communications,  listing and filing fees 13,517</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>0.01461</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.013738</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.011102</v>
+        <v>0.015523</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4721,26 +4749,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Interest income (3,637)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="n">
+      <c r="F41" s="5" t="n">
         <v>-0.000257</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4761,7 +4785,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Loss and comprehensive loss for the year (56,879)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4769,14 +4793,18 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n">
-        <v>-0.048866</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.047308</v>
-      </c>
-      <c r="G42" s="5" t="n">
         <v>-0.045268</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4797,22 +4825,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 5)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>-1e-08</v>
+          <t>Basic and diluted loss per common share (Note 5) (0.02)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F43" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="G43" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4828,12 +4856,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 3,530,000 303,981 47,231</t>
+          <t>Balance, July 31, 2023 3,630,000 328,354 37,858 (163,710)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4843,10 +4871,12 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.23481</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.116402</v>
+        <v>0.202502</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4862,12 +4892,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Exercise of warrants 100,000 24,373 (9,373)</t>
+          <t>Loss for the year - - - (45,268)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4877,7 +4907,7 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.015</v>
+        <v>-0.045268</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4898,29 +4928,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, July 31, 2024 3,630,000 328,354 37,858 (208,978)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.047308</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.047308</v>
+        <v>0.157234</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4936,12 +4964,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 3,630,000 328,354 37,858</t>
+          <t>Loss for the year - - - (56,879)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4951,10 +4979,12 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.202502</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.16371</v>
+        <v>-0.056879</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4970,12 +5000,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2024 3,630,000 328,354 37,858</t>
+          <t>Balance, July 31, 2025 3,630,000 328,354 37,858 (265,857)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4985,10 +5015,12 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.157234</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.208978</v>
+        <v>0.100355</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5004,27 +5036,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
+          <t>Administrative and corporate services (Note 6)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>7.7e-05</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0189</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0189</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5040,25 +5068,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 3,530,000 303,981 47,231</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Transfer  agent, shareholder communications,  listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
-        <v>0.283676</v>
+        <v>0.015279</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.067536</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01467</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.015523</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -5074,29 +5104,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>-0.048866</v>
+        <v>0.01461</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-0.048866</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013738</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.011102</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5112,25 +5140,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 3,530,000 303,981 47,231</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.23481</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>-0.116402</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.000257</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -5146,27 +5180,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Exercise of warrants 100,000 24,373 (9,373)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.048866</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-0.047308</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.045268</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -5182,27 +5216,417 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share (Note 5)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2022 3,530,000 303,981 47,231</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.116402</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Exercise of warrants 100,000 24,373 (9,373)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-0.047308</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.047308</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2023 3,630,000 328,354 37,858</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.202502</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.16371</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2024 3,630,000 328,354 37,858</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.157234</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.208978</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Office and sundry</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>7.7e-05</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2021 3,530,000 303,981 47,231</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>0.283676</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>-0.067536</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>-0.048866</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-0.048866</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2022 3,530,000 303,981 47,231</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-0.116402</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Exercise of warrants 100,000 24,373 (9,373)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>Balance, July 31, 2023 3,630,000 328,354 37,858</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
         <v>0.202502</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F65" s="5" t="n">
         <v>-0.16371</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
